--- a/input/old/Metadata _Canceled Jobs_SW_01_01_JOBS_CANC_N.xlsx
+++ b/input/old/Metadata _Canceled Jobs_SW_01_01_JOBS_CANC_N.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>05.09.2024 at 10:43 by ILIYAR</t>
+          <t>05.09.2024 at 10:43 by REDACTED</t>
         </is>
       </c>
     </row>
